--- a/artfynd/A 39834-2025 artfynd.xlsx
+++ b/artfynd/A 39834-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115608486</v>
+        <v>88278050</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korsbottnen, Upl</t>
+          <t>Hjortronmossen 1,4 km NO om Stenringen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659302</v>
+        <v>659428</v>
       </c>
       <c r="R2" t="n">
-        <v>6669891</v>
+        <v>6669732</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2020-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,61 +761,86 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandsumpskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gran, tall, klibbal och björk som står i en vitmossedominerad mark.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115608543</v>
+        <v>115608442</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659308</v>
+        <v>659273</v>
       </c>
       <c r="R3" t="n">
-        <v>6669839</v>
+        <v>6669712</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,58 +920,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115596999</v>
+        <v>115608445</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hjortronmossen, Hjortronmossen, Upl</t>
+          <t>Korsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659383</v>
+        <v>659276</v>
       </c>
       <c r="R4" t="n">
-        <v>6669751</v>
+        <v>6669717</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,14 +991,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Natträd med spillning under. Indikation på lekplats.</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,74 +1018,72 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115595345</v>
+        <v>115608406</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Korsbottnen (Korsbottnen), Upl</t>
+          <t>Korsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659315</v>
+        <v>659299</v>
       </c>
       <c r="R5" t="n">
-        <v>6669875</v>
+        <v>6669890</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,9 +1110,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,27 +1137,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115596632</v>
+        <v>115608413</v>
       </c>
       <c r="B6" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,37 +1160,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hjortronmossen (Hjortronmossen), Upl</t>
+          <t>Korsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659369</v>
+        <v>659303</v>
       </c>
       <c r="R6" t="n">
-        <v>6669836</v>
+        <v>6669813</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,9 +1229,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,27 +1256,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115608379</v>
+        <v>115596999</v>
       </c>
       <c r="B7" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,46 +1279,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Korsbottnen, Upl</t>
+          <t>Hjortronmossen, Hjortronmossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659373</v>
+        <v>659383</v>
       </c>
       <c r="R7" t="n">
-        <v>6669863</v>
+        <v>6669751</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,19 +1341,14 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:21</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Natträd med spillning under. Indikation på lekplats.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,63 +1363,55 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115608473</v>
+        <v>115608378</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1413,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659331</v>
+        <v>659277</v>
       </c>
       <c r="R8" t="n">
-        <v>6669884</v>
+        <v>6669708</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1448,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1458,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,32 +1491,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115608406</v>
+        <v>115608379</v>
       </c>
       <c r="B9" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1518,16 +1519,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1537,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659299</v>
+        <v>659373</v>
       </c>
       <c r="R9" t="n">
-        <v>6669890</v>
+        <v>6669863</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1572,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,15 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115608476</v>
+        <v>115595345</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,26 +1637,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Korsbottnen, Upl</t>
+          <t>Korsbottnen, Korsbottnen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659317</v>
+        <v>659315</v>
       </c>
       <c r="R10" t="n">
-        <v>6669890</v>
+        <v>6669875</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,19 +1684,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,15 +1701,1447 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115595553</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>659292</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6669875</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115595686</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>659272</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6669862</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115596019</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>659307</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6669935</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>115608473</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>659331</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6669884</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115608476</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>659317</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6669890</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115608486</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>659302</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6669891</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>115608496</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>659294</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6669893</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115608499</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>659275</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6669725</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115595670</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>659272</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6669862</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115596632</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hjortronmossen, Hjortronmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>659369</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6669836</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115608463</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>659299</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6669791</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>115608542</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>659295</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6669898</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>115608543</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Korsbottnen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>659308</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6669839</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39834-2025 artfynd.xlsx
+++ b/artfynd/A 39834-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88278050</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608445</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608406</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608413</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115596999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1488,6 +1523,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608378</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1604,6 +1644,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1710,6 +1755,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115595345</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115595553</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115595686</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2028,6 +2088,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115596019</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608473</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2262,6 +2332,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608476</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2381,6 +2456,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608486</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608496</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2615,6 +2700,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608499</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2712,6 +2802,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115595670</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2809,6 +2904,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115596632</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2920,6 +3020,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608463</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3031,6 +3136,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608542</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3142,8 +3252,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608543</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>